--- a/reportes/Otras_Instituciones_GALLARA MARIA CECILIA.xlsx
+++ b/reportes/Otras_Instituciones_GALLARA MARIA CECILIA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="36">
   <si>
     <t>N.º DE COMPROBANTE</t>
   </si>
@@ -80,6 +80,12 @@
     <t>74522302158241</t>
   </si>
   <si>
+    <t>75012498917373</t>
+  </si>
+  <si>
+    <t>75042683589883</t>
+  </si>
+  <si>
     <t>20/12/2023</t>
   </si>
   <si>
@@ -105,6 +111,12 @@
   </si>
   <si>
     <t>24/12/2024</t>
+  </si>
+  <si>
+    <t>04/01/2025</t>
+  </si>
+  <si>
+    <t>22/01/2025</t>
   </si>
   <si>
     <t>27292552462</t>
@@ -480,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" customWidth="1"/>
@@ -540,16 +552,16 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3">
         <v>144899.4</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -569,16 +581,16 @@
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3">
         <v>121715.52</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -598,16 +610,16 @@
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="3">
         <v>109636.44</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -627,16 +639,16 @@
         <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G5" s="3">
         <v>219272.88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -656,16 +668,16 @@
         <v>16</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6" s="3">
         <v>287960.1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -685,16 +697,16 @@
         <v>17</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G7" s="3">
         <v>234514.8</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -714,16 +726,16 @@
         <v>18</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8" s="3">
         <v>236859.84</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -743,16 +755,16 @@
         <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G9" s="3">
         <v>296074.8</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -772,16 +784,74 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G10" s="3">
         <v>241142.16</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1">
+        <v>298</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="3">
+        <v>6578.16</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1">
+        <v>300</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="3">
+        <v>242347.92</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
